--- a/output/yearly_benthic_cover_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_97_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.2759433076229</v>
+        <v>45.51389732866081</v>
       </c>
       <c r="M2" t="n">
-        <v>99.21070935826708</v>
+        <v>98.36897809594652</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00688323885629</v>
+        <v>88.01332350379616</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88069170041203</v>
+        <v>45.93636770355065</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228714614293289</v>
+        <v>2.228688905617379</v>
       </c>
       <c r="E3" t="n">
-        <v>5.677968442376007</v>
+        <v>5.709912724950631</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429048714310965</v>
+        <v>0.7428963018724597</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95664878298007</v>
+        <v>33.97594917808612</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17362408583043</v>
+        <v>34.17322988613314</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583866995501038</v>
+        <v>6.539544620433547</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643155446444353</v>
+        <v>4.643101886702873</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99311676114371</v>
+        <v>11.98667649620385</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88986277913961</v>
+        <v>48.84221529056016</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636712406953</v>
+        <v>106.7652594903147</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16840189367512</v>
+        <v>86.99637304022734</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68218133749667</v>
+        <v>42.54876673312909</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18866762601707</v>
+        <v>2.179165649428334</v>
       </c>
       <c r="E4" t="n">
-        <v>6.492291559093752</v>
+        <v>6.493204462358474</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444668130844656</v>
+        <v>0.7444507629032887</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3464937155746</v>
+        <v>33.22097631885424</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24547340188541</v>
+        <v>34.24473509355128</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498091196241917</v>
+        <v>5.461023484986169</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65291758177791</v>
+        <v>4.652817268145554</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83159810632488</v>
+        <v>13.00362695977267</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30333536185898</v>
+        <v>44.26595228986397</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81711480568053</v>
+        <v>99.81834598276573</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.03659533177478</v>
+        <v>85.72246275671382</v>
       </c>
       <c r="C5" t="n">
-        <v>42.40373692912537</v>
+        <v>42.12236239405669</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133513658745148</v>
+        <v>2.116646307772714</v>
       </c>
       <c r="E5" t="n">
-        <v>7.093668874037437</v>
+        <v>7.066737237268364</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457906764735612</v>
+        <v>0.7457704838037031</v>
       </c>
       <c r="G5" t="n">
-        <v>32.50616903531737</v>
+        <v>32.26788054609527</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30637111778381</v>
+        <v>34.30544225497034</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589890241457686</v>
+        <v>4.558920403030289</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661191727959757</v>
+        <v>4.661065523773145</v>
       </c>
       <c r="K5" t="n">
-        <v>13.96340466822523</v>
+        <v>14.27753724328618</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48013364719826</v>
+        <v>43.44840526585197</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727524454885</v>
+        <v>99.84830490319484</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.67634392216087</v>
+        <v>84.15477848184312</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75637559071766</v>
+        <v>41.2625336893791</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067086600167043</v>
+        <v>2.039664174156028</v>
       </c>
       <c r="E6" t="n">
-        <v>7.511253187540644</v>
+        <v>7.443858624737766</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469153049085328</v>
+        <v>0.7468944155542911</v>
       </c>
       <c r="G6" t="n">
-        <v>31.4940877740571</v>
+        <v>31.09430219122092</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3581040257925</v>
+        <v>34.35714311549739</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830676374016725</v>
+        <v>3.804825863462406</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668220655678329</v>
+        <v>4.66809009721432</v>
       </c>
       <c r="K6" t="n">
-        <v>15.3236560778391</v>
+        <v>15.84522151815689</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79247138029164</v>
+        <v>42.76560811460207</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87250304884842</v>
+        <v>99.87336332213805</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.17548259812914</v>
+        <v>82.3808726211913</v>
       </c>
       <c r="C7" t="n">
-        <v>40.85051992792167</v>
+        <v>40.07926158160918</v>
       </c>
       <c r="D7" t="n">
-        <v>1.994102576386835</v>
+        <v>1.953003514180748</v>
       </c>
       <c r="E7" t="n">
-        <v>7.778768196294028</v>
+        <v>7.656712991960703</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478720691752401</v>
+        <v>0.7478538662002402</v>
       </c>
       <c r="G7" t="n">
-        <v>30.38210472948993</v>
+        <v>29.77317649636138</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40211518206104</v>
+        <v>34.40127784521105</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196319412376821</v>
+        <v>3.174761243525674</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67420043234525</v>
+        <v>4.674086663751501</v>
       </c>
       <c r="K7" t="n">
-        <v>16.82451740187085</v>
+        <v>17.61912737880871</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21855499315143</v>
+        <v>42.19592143226372</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89359232294396</v>
+        <v>99.8943103926816</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.02498760919077</v>
+        <v>87.36102122169446</v>
       </c>
       <c r="C8" t="n">
-        <v>43.14402058382834</v>
+        <v>42.41035014842357</v>
       </c>
       <c r="D8" t="n">
-        <v>1.998353475399543</v>
+        <v>1.957249684086588</v>
       </c>
       <c r="E8" t="n">
-        <v>9.60539417248892</v>
+        <v>9.512963177603751</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494663345245428</v>
+        <v>0.7494798308017209</v>
       </c>
       <c r="G8" t="n">
-        <v>30.88277823651363</v>
+        <v>30.28286494618372</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47545138812897</v>
+        <v>34.47607221687916</v>
       </c>
       <c r="I8" t="n">
-        <v>5.629379411356784</v>
+        <v>5.698142423628763</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684164590778392</v>
+        <v>4.684248942510755</v>
       </c>
       <c r="K8" t="n">
-        <v>11.97501239080921</v>
+        <v>12.63897877830554</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69372020565418</v>
+        <v>44.7611450550674</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81275318029174</v>
+        <v>99.81047398179651</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.13919411485074</v>
+        <v>85.23325823255809</v>
       </c>
       <c r="C9" t="n">
-        <v>42.13205697616392</v>
+        <v>41.16620331948788</v>
       </c>
       <c r="D9" t="n">
-        <v>1.913128162343911</v>
+        <v>1.86096290076552</v>
       </c>
       <c r="E9" t="n">
-        <v>9.979025730449258</v>
+        <v>9.837854595840188</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508293426722902</v>
+        <v>0.7508742357383074</v>
       </c>
       <c r="G9" t="n">
-        <v>29.56569671133035</v>
+        <v>28.79310118271419</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53814976292535</v>
+        <v>34.54021484396214</v>
       </c>
       <c r="I9" t="n">
-        <v>4.699681013427747</v>
+        <v>4.757286500173343</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692683391701814</v>
+        <v>4.692963973364421</v>
       </c>
       <c r="K9" t="n">
-        <v>13.86080588514927</v>
+        <v>14.76674176744188</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85076548837135</v>
+        <v>43.90877317908055</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84362834968454</v>
+        <v>99.84171826601032</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.05852409760884</v>
+        <v>82.89883054747409</v>
       </c>
       <c r="C10" t="n">
-        <v>40.7807434036411</v>
+        <v>39.56909946610936</v>
       </c>
       <c r="D10" t="n">
-        <v>1.819939299803349</v>
+        <v>1.756475188927694</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1466941296811</v>
+        <v>9.947276546212096</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519972284249447</v>
+        <v>0.7520730956959711</v>
       </c>
       <c r="G10" t="n">
-        <v>28.12554560123821</v>
+        <v>27.17645140530099</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59187250754746</v>
+        <v>34.59536240201467</v>
       </c>
       <c r="I10" t="n">
-        <v>3.922492653257879</v>
+        <v>3.970735061222859</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699982677655904</v>
+        <v>4.70045684809982</v>
       </c>
       <c r="K10" t="n">
-        <v>15.94147590239116</v>
+        <v>17.10116945252591</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14723399915029</v>
+        <v>43.19758423413768</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86945330518255</v>
+        <v>99.86785315277294</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.69291241004375</v>
+        <v>80.48226575532274</v>
       </c>
       <c r="C11" t="n">
-        <v>39.02335521786834</v>
+        <v>37.76720242471082</v>
       </c>
       <c r="D11" t="n">
-        <v>1.714842197444833</v>
+        <v>1.649563690830696</v>
       </c>
       <c r="E11" t="n">
-        <v>10.10626526413385</v>
+        <v>9.894062786883817</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530015461481792</v>
+        <v>0.7531052006492737</v>
       </c>
       <c r="G11" t="n">
-        <v>26.50136322039625</v>
+        <v>25.52230043805918</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63807112281624</v>
+        <v>34.64283922986659</v>
       </c>
       <c r="I11" t="n">
-        <v>3.273109395678282</v>
+        <v>3.313486904975238</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70625966342612</v>
+        <v>4.706907504057961</v>
       </c>
       <c r="K11" t="n">
-        <v>18.30708758995624</v>
+        <v>19.51773424467724</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56059906291826</v>
+        <v>42.60476513446687</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89104187074284</v>
+        <v>99.88970180385493</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.33839076965019</v>
+        <v>77.93227222683946</v>
       </c>
       <c r="C12" t="n">
-        <v>37.17554911490708</v>
+        <v>35.72924510251956</v>
       </c>
       <c r="D12" t="n">
-        <v>1.611329324143389</v>
+        <v>1.537896359741423</v>
       </c>
       <c r="E12" t="n">
-        <v>9.951341718783086</v>
+        <v>9.685034185111615</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538654560982243</v>
+        <v>0.7539957013977658</v>
       </c>
       <c r="G12" t="n">
-        <v>24.90166369268699</v>
+        <v>23.79456649906744</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67781098051832</v>
+        <v>34.68380226429723</v>
       </c>
       <c r="I12" t="n">
-        <v>2.730720496806289</v>
+        <v>2.764504083487952</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711659100613901</v>
+        <v>4.712473133736037</v>
       </c>
       <c r="K12" t="n">
-        <v>20.66160923034981</v>
+        <v>22.06772777316054</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07192194930759</v>
+        <v>42.11098582140391</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90908029456448</v>
+        <v>99.90795869708403</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.83381899322009</v>
+        <v>75.46012122410498</v>
       </c>
       <c r="C13" t="n">
-        <v>35.09289515094915</v>
+        <v>33.68330064306821</v>
       </c>
       <c r="D13" t="n">
-        <v>1.502137300960311</v>
+        <v>1.430780608385323</v>
       </c>
       <c r="E13" t="n">
-        <v>9.656628779363126</v>
+        <v>9.394813590028342</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546104369956731</v>
+        <v>0.7547637846400794</v>
       </c>
       <c r="G13" t="n">
-        <v>23.21419794717617</v>
+        <v>22.13725529431965</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71208010180096</v>
+        <v>34.71913409344365</v>
       </c>
       <c r="I13" t="n">
-        <v>2.277849195700896</v>
+        <v>2.306100199287449</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716315231222956</v>
+        <v>4.717273654000498</v>
       </c>
       <c r="K13" t="n">
-        <v>23.1661810067799</v>
+        <v>24.53987877589501</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66507049513746</v>
+        <v>41.7000288009399</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92414665286651</v>
+        <v>99.9232082199031</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.60349779715459</v>
+        <v>82.64898377422355</v>
       </c>
       <c r="C14" t="n">
-        <v>39.17934739755797</v>
+        <v>38.17672368577897</v>
       </c>
       <c r="D14" t="n">
-        <v>1.504011946715544</v>
+        <v>1.432487248855462</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95793476514988</v>
+        <v>11.88469442861114</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75555217997194</v>
+        <v>0.7556640697101404</v>
       </c>
       <c r="G14" t="n">
-        <v>25.01074376798767</v>
+        <v>24.14941527764472</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52297511423532</v>
+        <v>36.74630178893865</v>
       </c>
       <c r="I14" t="n">
-        <v>3.130078898269602</v>
+        <v>2.957520524775064</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722201124824625</v>
+        <v>4.72290043568838</v>
       </c>
       <c r="K14" t="n">
-        <v>16.39650220284543</v>
+        <v>17.35101622577643</v>
       </c>
       <c r="L14" t="n">
-        <v>44.31994448380568</v>
+        <v>44.37379352224119</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89579408420907</v>
+        <v>99.90153343379659</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.73928492806019</v>
+        <v>81.82308851802594</v>
       </c>
       <c r="C15" t="n">
-        <v>38.79876297104587</v>
+        <v>37.80309425261913</v>
       </c>
       <c r="D15" t="n">
-        <v>1.471773908841641</v>
+        <v>1.401854523933161</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13681057705745</v>
+        <v>12.04577055131865</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75634698773874</v>
+        <v>0.7564235463798544</v>
       </c>
       <c r="G15" t="n">
-        <v>24.47464609495545</v>
+        <v>23.63703945559643</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56139568273731</v>
+        <v>36.78727580336852</v>
       </c>
       <c r="I15" t="n">
-        <v>2.611143003362487</v>
+        <v>2.467077472555243</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727168673367124</v>
+        <v>4.727647164874092</v>
       </c>
       <c r="K15" t="n">
-        <v>17.26071507193981</v>
+        <v>18.17691148197406</v>
       </c>
       <c r="L15" t="n">
-        <v>43.85357532095128</v>
+        <v>43.93784091749639</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91305336393697</v>
+        <v>99.91784665208958</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.19838442479083</v>
+        <v>79.22035754434313</v>
       </c>
       <c r="C16" t="n">
-        <v>36.66133581579095</v>
+        <v>35.5810067525113</v>
       </c>
       <c r="D16" t="n">
-        <v>1.374821035997193</v>
+        <v>1.304596035576335</v>
       </c>
       <c r="E16" t="n">
-        <v>11.70028714244636</v>
+        <v>11.55300002610136</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570316502898053</v>
+        <v>0.7570784605377404</v>
       </c>
       <c r="G16" t="n">
-        <v>22.8623826647492</v>
+        <v>21.99713839066142</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59449189234012</v>
+        <v>36.81912635570654</v>
       </c>
       <c r="I16" t="n">
-        <v>2.177922224656879</v>
+        <v>2.057677897398857</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731447814311283</v>
+        <v>4.73174037836088</v>
       </c>
       <c r="K16" t="n">
-        <v>19.80161557520915</v>
+        <v>20.77964245565686</v>
       </c>
       <c r="L16" t="n">
-        <v>43.46451685890651</v>
+        <v>43.57082086203864</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92746824990661</v>
+        <v>99.93147007020681</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.79187875850793</v>
+        <v>81.08705262919804</v>
       </c>
       <c r="C17" t="n">
-        <v>37.81644022996286</v>
+        <v>36.93246503727671</v>
       </c>
       <c r="D17" t="n">
-        <v>1.376053922778983</v>
+        <v>1.305694045041547</v>
       </c>
       <c r="E17" t="n">
-        <v>12.45561097644286</v>
+        <v>12.39422210472593</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577105272422244</v>
+        <v>0.7577156534257378</v>
       </c>
       <c r="G17" t="n">
-        <v>23.26097713686665</v>
+        <v>22.50591733604202</v>
       </c>
       <c r="H17" t="n">
-        <v>37.00540079339742</v>
+        <v>37.3403801842196</v>
       </c>
       <c r="I17" t="n">
-        <v>2.200434606515891</v>
+        <v>2.047400471832328</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735690795263902</v>
+        <v>4.735722833910863</v>
       </c>
       <c r="K17" t="n">
-        <v>18.20812124149206</v>
+        <v>18.91294737080198</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90215642490809</v>
+        <v>44.08639830084572</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92671789636302</v>
+        <v>99.9318107089244</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.46795431535418</v>
+        <v>78.58240806864652</v>
       </c>
       <c r="C18" t="n">
-        <v>35.83204403774863</v>
+        <v>34.74326575532712</v>
       </c>
       <c r="D18" t="n">
-        <v>1.290834383976377</v>
+        <v>1.216249068411499</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99008145210181</v>
+        <v>11.82973817532938</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582937727759804</v>
+        <v>0.7582644301070621</v>
       </c>
       <c r="G18" t="n">
-        <v>21.82041604337516</v>
+        <v>20.96417694302675</v>
       </c>
       <c r="H18" t="n">
-        <v>37.03388559591977</v>
+        <v>37.36742400972887</v>
       </c>
       <c r="I18" t="n">
-        <v>1.835106987355207</v>
+        <v>1.707402753873802</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739336079849877</v>
+        <v>4.73915268816914</v>
       </c>
       <c r="K18" t="n">
-        <v>20.53204568464582</v>
+        <v>21.41759193135348</v>
       </c>
       <c r="L18" t="n">
-        <v>43.57478709409123</v>
+        <v>43.78227007799074</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93887681648567</v>
+        <v>99.94312776467135</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.54401191593342</v>
+        <v>77.58220350755985</v>
       </c>
       <c r="C19" t="n">
-        <v>35.19055922327458</v>
+        <v>33.99904823505183</v>
       </c>
       <c r="D19" t="n">
-        <v>1.257673084157195</v>
+        <v>1.180943190657243</v>
       </c>
       <c r="E19" t="n">
-        <v>11.93709993993557</v>
+        <v>11.72464284306904</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587862262962067</v>
+        <v>0.7587302522821759</v>
       </c>
       <c r="G19" t="n">
-        <v>21.25985353622793</v>
+        <v>20.35561847618591</v>
       </c>
       <c r="H19" t="n">
-        <v>37.05793625805643</v>
+        <v>37.3903798204454</v>
       </c>
       <c r="I19" t="n">
-        <v>1.530248956908799</v>
+        <v>1.42982484815649</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742413914351291</v>
+        <v>4.742064076763602</v>
       </c>
       <c r="K19" t="n">
-        <v>21.45598808406658</v>
+        <v>22.41779649244013</v>
       </c>
       <c r="L19" t="n">
-        <v>43.30247749856565</v>
+        <v>43.53552370558512</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9490248059068</v>
+        <v>99.95236843307708</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.9257889634776</v>
+        <v>74.90200282253494</v>
       </c>
       <c r="C20" t="n">
-        <v>32.80772441150953</v>
+        <v>31.53832086163562</v>
       </c>
       <c r="D20" t="n">
-        <v>1.162752891931688</v>
+        <v>1.086358382777082</v>
       </c>
       <c r="E20" t="n">
-        <v>11.24882642614509</v>
+        <v>10.98427788310677</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759211269350622</v>
+        <v>0.7591327882190385</v>
       </c>
       <c r="G20" t="n">
-        <v>19.65531145787281</v>
+        <v>18.72528411456402</v>
       </c>
       <c r="H20" t="n">
-        <v>37.07869469814348</v>
+        <v>37.41021687258007</v>
       </c>
       <c r="I20" t="n">
-        <v>1.275921786592533</v>
+        <v>1.192152854918966</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745070433441386</v>
+        <v>4.744579926368993</v>
       </c>
       <c r="K20" t="n">
-        <v>24.07421103652239</v>
+        <v>25.09799717746505</v>
       </c>
       <c r="L20" t="n">
-        <v>43.07555763649838</v>
+        <v>43.32396460400609</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95749308453031</v>
+        <v>99.96028264310675</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.74951634506968</v>
+        <v>81.18831008741405</v>
       </c>
       <c r="C21" t="n">
-        <v>36.35861208027632</v>
+        <v>35.49183022765729</v>
       </c>
       <c r="D21" t="n">
-        <v>1.163652345947144</v>
+        <v>1.087097545721109</v>
       </c>
       <c r="E21" t="n">
-        <v>13.18324382402206</v>
+        <v>13.0995816565314</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597985614825403</v>
+        <v>0.7596493054527097</v>
       </c>
       <c r="G21" t="n">
-        <v>21.28004275694778</v>
+        <v>20.56965051480273</v>
       </c>
       <c r="H21" t="n">
-        <v>38.71690395296213</v>
+        <v>39.26729658191211</v>
       </c>
       <c r="I21" t="n">
-        <v>1.897133894442162</v>
+        <v>1.657226323914551</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748741009265875</v>
+        <v>4.747808159079438</v>
       </c>
       <c r="K21" t="n">
-        <v>18.25048365493031</v>
+        <v>18.81168991258596</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32771534845229</v>
+        <v>45.64127654286858</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93681108365894</v>
+        <v>99.94479668311183</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_97_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.51389732866081</v>
+        <v>45.75383154587492</v>
       </c>
       <c r="M2" t="n">
-        <v>98.36897809594652</v>
+        <v>99.65388291143637</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01332350379616</v>
+        <v>87.97552621718266</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93636770355065</v>
+        <v>45.85865937297486</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228688905617379</v>
+        <v>2.22865084586074</v>
       </c>
       <c r="E3" t="n">
-        <v>5.709912724950631</v>
+        <v>5.663700902194718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428963018724597</v>
+        <v>0.7428836152869134</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97594917808612</v>
+        <v>33.94932297066595</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17322988613314</v>
+        <v>34.17264630319801</v>
       </c>
       <c r="I3" t="n">
-        <v>6.539544620433547</v>
+        <v>6.575298984433103</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643101886702873</v>
+        <v>4.643022595543209</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98667649620385</v>
+        <v>12.02447378281735</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84221529056016</v>
+        <v>48.88083888149141</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652594903147</v>
+        <v>106.7639720372836</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99637304022734</v>
+        <v>87.09059327370393</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54876673312909</v>
+        <v>42.61286136058976</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179165649428334</v>
+        <v>2.186100574870353</v>
       </c>
       <c r="E4" t="n">
-        <v>6.493204462358474</v>
+        <v>6.470722558122849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444507629032887</v>
+        <v>0.7444448719260388</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22097631885424</v>
+        <v>33.30114925829419</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24473509355128</v>
+        <v>34.24446410859778</v>
       </c>
       <c r="I4" t="n">
-        <v>5.461023484986169</v>
+        <v>5.490931452354988</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652817268145554</v>
+        <v>4.652780449537743</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00362695977267</v>
+        <v>12.90940672629606</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26595228986397</v>
+        <v>44.29508471910214</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81834598276573</v>
+        <v>99.81735280598795</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.72246275671382</v>
+        <v>85.94108599963286</v>
       </c>
       <c r="C5" t="n">
-        <v>42.12236239405669</v>
+        <v>42.315539357525</v>
       </c>
       <c r="D5" t="n">
-        <v>2.116646307772714</v>
+        <v>2.129989020230313</v>
       </c>
       <c r="E5" t="n">
-        <v>7.066737237268364</v>
+        <v>7.068621093578994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457704838037031</v>
+        <v>0.7457684412262791</v>
       </c>
       <c r="G5" t="n">
-        <v>32.26788054609527</v>
+        <v>32.44639478008647</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30544225497034</v>
+        <v>34.30534829640883</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558920403030289</v>
+        <v>4.583911610437741</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661065523773145</v>
+        <v>4.661052757664244</v>
       </c>
       <c r="K5" t="n">
-        <v>14.27753724328618</v>
+        <v>14.05891400036713</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44840526585197</v>
+        <v>43.47302076843135</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84830490319484</v>
+        <v>99.84747412632348</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.15477848184312</v>
+        <v>84.72513990897583</v>
       </c>
       <c r="C6" t="n">
-        <v>41.2625336893791</v>
+        <v>41.81148163480359</v>
       </c>
       <c r="D6" t="n">
-        <v>2.039664174156028</v>
+        <v>2.070910153302933</v>
       </c>
       <c r="E6" t="n">
-        <v>7.443858624737766</v>
+        <v>7.510173508631984</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468944155542911</v>
+        <v>0.746890921247267</v>
       </c>
       <c r="G6" t="n">
-        <v>31.09430219122092</v>
+        <v>31.54643885483072</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35714311549739</v>
+        <v>34.35698237737427</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804825863462406</v>
+        <v>3.825675835793248</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66809009721432</v>
+        <v>4.668068257795418</v>
       </c>
       <c r="K6" t="n">
-        <v>15.84522151815689</v>
+        <v>15.27486009102417</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76560811460207</v>
+        <v>42.78632739610453</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87336332213805</v>
+        <v>99.87266912193228</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.3808726211913</v>
+        <v>83.24508513902657</v>
       </c>
       <c r="C7" t="n">
-        <v>40.07926158160918</v>
+        <v>40.92570253414605</v>
       </c>
       <c r="D7" t="n">
-        <v>1.953003514180748</v>
+        <v>1.998936175485994</v>
       </c>
       <c r="E7" t="n">
-        <v>7.656712991960703</v>
+        <v>7.781182292664165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478538662002402</v>
+        <v>0.7478456038539837</v>
       </c>
       <c r="G7" t="n">
-        <v>29.77317649636138</v>
+        <v>30.45005005847483</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40127784521105</v>
+        <v>34.40089777728324</v>
       </c>
       <c r="I7" t="n">
-        <v>3.174761243525674</v>
+        <v>3.192138207176956</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674086663751501</v>
+        <v>4.674035024087397</v>
       </c>
       <c r="K7" t="n">
-        <v>17.61912737880871</v>
+        <v>16.75491486097342</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19592143226372</v>
+        <v>42.21311383166407</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8943103926816</v>
+        <v>99.89373122678354</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.36102122169446</v>
+        <v>87.97529079115441</v>
       </c>
       <c r="C8" t="n">
-        <v>42.41035014842357</v>
+        <v>43.17741129784152</v>
       </c>
       <c r="D8" t="n">
-        <v>1.957249684086588</v>
+        <v>2.003139651014024</v>
       </c>
       <c r="E8" t="n">
-        <v>9.512963177603751</v>
+        <v>9.575225447231382</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494798308017209</v>
+        <v>0.7494182156927687</v>
       </c>
       <c r="G8" t="n">
-        <v>30.28286494618372</v>
+        <v>30.9404238752279</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47607221687916</v>
+        <v>34.47323792186735</v>
       </c>
       <c r="I8" t="n">
-        <v>5.698142423628763</v>
+        <v>5.549981832041175</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684248942510755</v>
+        <v>4.683863848079803</v>
       </c>
       <c r="K8" t="n">
-        <v>12.63897877830554</v>
+        <v>12.02470920884559</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7611450550674</v>
+        <v>44.61326830970184</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81047398179651</v>
+        <v>99.81538881638895</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.23325823255809</v>
+        <v>85.76888901050019</v>
       </c>
       <c r="C9" t="n">
-        <v>41.16620331948788</v>
+        <v>41.83263621851756</v>
       </c>
       <c r="D9" t="n">
-        <v>1.86096290076552</v>
+        <v>1.902611806498794</v>
       </c>
       <c r="E9" t="n">
-        <v>9.837854595840188</v>
+        <v>9.866910256953908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508742357383074</v>
+        <v>0.7507676907153247</v>
       </c>
       <c r="G9" t="n">
-        <v>28.79310118271419</v>
+        <v>29.38767436073964</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54021484396214</v>
+        <v>34.53531377290493</v>
       </c>
       <c r="I9" t="n">
-        <v>4.757286500173343</v>
+        <v>4.633313055716808</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692963973364421</v>
+        <v>4.692298066970778</v>
       </c>
       <c r="K9" t="n">
-        <v>14.76674176744188</v>
+        <v>14.23111098949983</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90877317908055</v>
+        <v>43.78208662998146</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84171826601032</v>
+        <v>99.84583383799885</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.89883054747409</v>
+        <v>83.35236153796588</v>
       </c>
       <c r="C10" t="n">
-        <v>39.56909946610936</v>
+        <v>40.13495234455627</v>
       </c>
       <c r="D10" t="n">
-        <v>1.756475188927694</v>
+        <v>1.79367033439822</v>
       </c>
       <c r="E10" t="n">
-        <v>9.947276546212096</v>
+        <v>9.946452644008984</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520730956959711</v>
+        <v>0.7519287326761553</v>
       </c>
       <c r="G10" t="n">
-        <v>27.17645140530099</v>
+        <v>27.70496825351603</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59536240201467</v>
+        <v>34.58872170310314</v>
       </c>
       <c r="I10" t="n">
-        <v>3.970735061222859</v>
+        <v>3.867065291037382</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70045684809982</v>
+        <v>4.69955457922597</v>
       </c>
       <c r="K10" t="n">
-        <v>17.10116945252591</v>
+        <v>16.64763846203412</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19758423413768</v>
+        <v>43.08870605297304</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86785315277294</v>
+        <v>99.87129685956343</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.48226575532274</v>
+        <v>80.70773534611976</v>
       </c>
       <c r="C11" t="n">
-        <v>37.76720242471082</v>
+        <v>38.08948617428625</v>
       </c>
       <c r="D11" t="n">
-        <v>1.649563690830696</v>
+        <v>1.675642547611905</v>
       </c>
       <c r="E11" t="n">
-        <v>9.894062786883817</v>
+        <v>9.829760533691005</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7531052006492737</v>
+        <v>0.7529308508427303</v>
       </c>
       <c r="G11" t="n">
-        <v>25.52230043805918</v>
+        <v>25.88191525250584</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64283922986659</v>
+        <v>34.63481913876559</v>
       </c>
       <c r="I11" t="n">
-        <v>3.313486904975238</v>
+        <v>3.226849204935627</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706907504057961</v>
+        <v>4.705817817767064</v>
       </c>
       <c r="K11" t="n">
-        <v>19.51773424467724</v>
+        <v>19.29226465388023</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60476513446687</v>
+        <v>42.51083069152693</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88970180385493</v>
+        <v>99.89258151969341</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.93227222683946</v>
+        <v>77.95931350777032</v>
       </c>
       <c r="C12" t="n">
-        <v>35.72924510251956</v>
+        <v>35.84000084698754</v>
       </c>
       <c r="D12" t="n">
-        <v>1.537896359741423</v>
+        <v>1.554249493309464</v>
       </c>
       <c r="E12" t="n">
-        <v>9.685034185111615</v>
+        <v>9.566326290243213</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539957013977658</v>
+        <v>0.7537975390334699</v>
       </c>
       <c r="G12" t="n">
-        <v>23.79456649906744</v>
+        <v>24.00688244901421</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68380226429723</v>
+        <v>34.67468679553961</v>
       </c>
       <c r="I12" t="n">
-        <v>2.764504083487952</v>
+        <v>2.692136321671164</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712473133736037</v>
+        <v>4.711234618959186</v>
       </c>
       <c r="K12" t="n">
-        <v>22.06772777316054</v>
+        <v>22.04068649222968</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11098582140391</v>
+        <v>42.02967796064567</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90795869708403</v>
+        <v>99.91036529986289</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.46012122410498</v>
+        <v>75.11827916589367</v>
       </c>
       <c r="C13" t="n">
-        <v>33.68330064306821</v>
+        <v>33.41412925217804</v>
       </c>
       <c r="D13" t="n">
-        <v>1.430780608385323</v>
+        <v>1.429968648602906</v>
       </c>
       <c r="E13" t="n">
-        <v>9.394813590028342</v>
+        <v>9.175664460525295</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547637846400794</v>
+        <v>0.7545487055046503</v>
       </c>
       <c r="G13" t="n">
-        <v>22.13725529431965</v>
+        <v>22.08724493754778</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71913409344365</v>
+        <v>34.70924045321391</v>
       </c>
       <c r="I13" t="n">
-        <v>2.306100199287449</v>
+        <v>2.245682551095054</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717273654000498</v>
+        <v>4.715929409404064</v>
       </c>
       <c r="K13" t="n">
-        <v>24.53987877589501</v>
+        <v>24.88172083410633</v>
       </c>
       <c r="L13" t="n">
-        <v>41.7000288009399</v>
+        <v>41.62936834922477</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9232082199031</v>
+        <v>99.92521843550914</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.64898377422355</v>
+        <v>82.4275505795307</v>
       </c>
       <c r="C14" t="n">
-        <v>38.17672368577897</v>
+        <v>38.02826262728247</v>
       </c>
       <c r="D14" t="n">
-        <v>1.432487248855462</v>
+        <v>1.431604107644312</v>
       </c>
       <c r="E14" t="n">
-        <v>11.88469442861114</v>
+        <v>11.71487772349513</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556640697101404</v>
+        <v>0.7554116849159852</v>
       </c>
       <c r="G14" t="n">
-        <v>24.14941527764472</v>
+        <v>24.16986213885637</v>
       </c>
       <c r="H14" t="n">
-        <v>36.74630178893865</v>
+        <v>36.80629346520048</v>
       </c>
       <c r="I14" t="n">
-        <v>2.957520524775064</v>
+        <v>2.828178428693537</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72290043568838</v>
+        <v>4.721323030724907</v>
       </c>
       <c r="K14" t="n">
-        <v>17.35101622577643</v>
+        <v>17.5724494204693</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37379352224119</v>
+        <v>44.30512303463141</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90153343379659</v>
+        <v>99.90583508238316</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.82308851802594</v>
+        <v>81.28269531170031</v>
       </c>
       <c r="C15" t="n">
-        <v>37.80309425261913</v>
+        <v>37.31970294662219</v>
       </c>
       <c r="D15" t="n">
-        <v>1.401854523933161</v>
+        <v>1.389025390084829</v>
       </c>
       <c r="E15" t="n">
-        <v>12.04577055131865</v>
+        <v>11.75963682851219</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564235463798544</v>
+        <v>0.756142503966206</v>
       </c>
       <c r="G15" t="n">
-        <v>23.63703945559643</v>
+        <v>23.45100297383524</v>
       </c>
       <c r="H15" t="n">
-        <v>36.78727580336852</v>
+        <v>36.84190151968189</v>
       </c>
       <c r="I15" t="n">
-        <v>2.467077472555243</v>
+        <v>2.359095445831168</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727647164874092</v>
+        <v>4.725890649788787</v>
       </c>
       <c r="K15" t="n">
-        <v>18.17691148197406</v>
+        <v>18.71730468829967</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93784091749639</v>
+        <v>43.88443185317</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91784665208958</v>
+        <v>99.92143948809186</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.22035754434313</v>
+        <v>78.52905989839776</v>
       </c>
       <c r="C16" t="n">
-        <v>35.5810067525113</v>
+        <v>34.92982442835022</v>
       </c>
       <c r="D16" t="n">
-        <v>1.304596035576335</v>
+        <v>1.285592595944172</v>
       </c>
       <c r="E16" t="n">
-        <v>11.55300002610136</v>
+        <v>11.21188957250816</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570784605377404</v>
+        <v>0.7567740119170161</v>
       </c>
       <c r="G16" t="n">
-        <v>21.99713839066142</v>
+        <v>21.70474060865521</v>
       </c>
       <c r="H16" t="n">
-        <v>36.81912635570654</v>
+        <v>36.87267079083198</v>
       </c>
       <c r="I16" t="n">
-        <v>2.057677897398857</v>
+        <v>1.967554744059863</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73174037836088</v>
+        <v>4.72983757448135</v>
       </c>
       <c r="K16" t="n">
-        <v>20.77964245565686</v>
+        <v>21.47094010160225</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57082086203864</v>
+        <v>43.53370504099665</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93147007020681</v>
+        <v>99.93446957094912</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.08705262919804</v>
+        <v>80.1910016820549</v>
       </c>
       <c r="C17" t="n">
-        <v>36.93246503727671</v>
+        <v>36.14275937358919</v>
       </c>
       <c r="D17" t="n">
-        <v>1.305694045041547</v>
+        <v>1.286636259456425</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39422210472593</v>
+        <v>11.9761040143622</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577156534257378</v>
+        <v>0.7573883725050835</v>
       </c>
       <c r="G17" t="n">
-        <v>22.50591733604202</v>
+        <v>22.15197196593579</v>
       </c>
       <c r="H17" t="n">
-        <v>37.3403801842196</v>
+        <v>37.33221570322907</v>
       </c>
       <c r="I17" t="n">
-        <v>2.047400471832328</v>
+        <v>1.953008038409574</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735722833910863</v>
+        <v>4.733677328156772</v>
       </c>
       <c r="K17" t="n">
-        <v>18.91294737080198</v>
+        <v>19.80899831794508</v>
       </c>
       <c r="L17" t="n">
-        <v>44.08639830084572</v>
+        <v>43.98319484703169</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9318107089244</v>
+        <v>99.93495253856597</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.58240806864652</v>
+        <v>77.5838724786571</v>
       </c>
       <c r="C18" t="n">
-        <v>34.74326575532712</v>
+        <v>33.83622252530744</v>
       </c>
       <c r="D18" t="n">
-        <v>1.216249068411499</v>
+        <v>1.192751827654342</v>
       </c>
       <c r="E18" t="n">
-        <v>11.82973817532938</v>
+        <v>11.37366180559635</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582644301070621</v>
+        <v>0.7579183439808851</v>
       </c>
       <c r="G18" t="n">
-        <v>20.96417694302675</v>
+        <v>20.53556695167311</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36742400972887</v>
+        <v>37.35833837710343</v>
       </c>
       <c r="I18" t="n">
-        <v>1.707402753873802</v>
+        <v>1.628645522768446</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73915268816914</v>
+        <v>4.736989649880532</v>
       </c>
       <c r="K18" t="n">
-        <v>21.41759193135348</v>
+        <v>22.41612752134291</v>
       </c>
       <c r="L18" t="n">
-        <v>43.78227007799074</v>
+        <v>43.69339973006048</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94312776467135</v>
+        <v>99.94574977671084</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.58220350755985</v>
+        <v>76.50404817875599</v>
       </c>
       <c r="C19" t="n">
-        <v>33.99904823505183</v>
+        <v>32.9878965336159</v>
       </c>
       <c r="D19" t="n">
-        <v>1.180943190657243</v>
+        <v>1.153765065410313</v>
       </c>
       <c r="E19" t="n">
-        <v>11.72464284306904</v>
+        <v>11.23120022994918</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587302522821759</v>
+        <v>0.7583726795483686</v>
       </c>
       <c r="G19" t="n">
-        <v>20.35561847618591</v>
+        <v>19.86433321492359</v>
       </c>
       <c r="H19" t="n">
-        <v>37.3903798204454</v>
+        <v>37.38073290284832</v>
       </c>
       <c r="I19" t="n">
-        <v>1.42982484815649</v>
+        <v>1.375814838898938</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742064076763602</v>
+        <v>4.739829247177304</v>
       </c>
       <c r="K19" t="n">
-        <v>22.41779649244013</v>
+        <v>23.49595182124398</v>
       </c>
       <c r="L19" t="n">
-        <v>43.53552370558512</v>
+        <v>43.47031862519961</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95236843307708</v>
+        <v>99.95416698005948</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.90200282253494</v>
+        <v>73.76948812334695</v>
       </c>
       <c r="C20" t="n">
-        <v>31.53832086163562</v>
+        <v>30.46419652871391</v>
       </c>
       <c r="D20" t="n">
-        <v>1.086358382777082</v>
+        <v>1.056479564649205</v>
       </c>
       <c r="E20" t="n">
-        <v>10.98427788310677</v>
+        <v>10.47536956964155</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591327882190385</v>
+        <v>0.7587657663362092</v>
       </c>
       <c r="G20" t="n">
-        <v>18.72528411456402</v>
+        <v>18.1893721140585</v>
       </c>
       <c r="H20" t="n">
-        <v>37.41021687258007</v>
+        <v>37.40010843234742</v>
       </c>
       <c r="I20" t="n">
-        <v>1.192152854918966</v>
+        <v>1.147106636712753</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744579926368993</v>
+        <v>4.742286039601307</v>
       </c>
       <c r="K20" t="n">
-        <v>25.09799717746505</v>
+        <v>26.23051187665304</v>
       </c>
       <c r="L20" t="n">
-        <v>43.32396460400609</v>
+        <v>43.26707451577474</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96028264310675</v>
+        <v>99.96178292114169</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.18831008741405</v>
+        <v>80.16821531783935</v>
       </c>
       <c r="C21" t="n">
-        <v>35.49183022765729</v>
+        <v>34.52983336107012</v>
       </c>
       <c r="D21" t="n">
-        <v>1.087097545721109</v>
+        <v>1.057160217073039</v>
       </c>
       <c r="E21" t="n">
-        <v>13.0995816565314</v>
+        <v>12.63747010487629</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596493054527097</v>
+        <v>0.759254612287669</v>
       </c>
       <c r="G21" t="n">
-        <v>20.56965051480273</v>
+        <v>20.09819477740934</v>
       </c>
       <c r="H21" t="n">
-        <v>39.26729658191211</v>
+        <v>39.32130789377009</v>
       </c>
       <c r="I21" t="n">
-        <v>1.657226323914551</v>
+        <v>1.549486385624996</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747808159079438</v>
+        <v>4.745341326797932</v>
       </c>
       <c r="K21" t="n">
-        <v>18.81168991258596</v>
+        <v>19.83178468216065</v>
       </c>
       <c r="L21" t="n">
-        <v>45.64127654286858</v>
+        <v>45.58676566513314</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94479668311183</v>
+        <v>99.94838370836391</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_97_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.75383154587492</v>
+        <v>43.54474046000047</v>
       </c>
       <c r="M2" t="n">
-        <v>99.65388291143637</v>
+        <v>95.87854541995787</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.97552621718266</v>
+        <v>81.47410234782284</v>
       </c>
       <c r="C3" t="n">
-        <v>45.85865937297486</v>
+        <v>43.22965790337839</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22865084586074</v>
+        <v>2.180303726543814</v>
       </c>
       <c r="E3" t="n">
-        <v>5.663700902194718</v>
+        <v>4.146083296513544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428836152869134</v>
+        <v>0.73763100327435</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94932297066595</v>
+        <v>32.79540188676321</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17264630319801</v>
+        <v>33.9310261506201</v>
       </c>
       <c r="I3" t="n">
-        <v>6.575298984433103</v>
+        <v>3.073462513643125</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643022595543209</v>
+        <v>4.610193770464687</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02447378281735</v>
+        <v>18.52589765217717</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88083888149141</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639720372836</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09059327370393</v>
+        <v>88.65724873738348</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61286136058976</v>
+        <v>42.87206015108085</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186100574870353</v>
+        <v>2.186065601244874</v>
       </c>
       <c r="E4" t="n">
-        <v>6.470722558122849</v>
+        <v>6.561264512512833</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444448719260388</v>
+        <v>0.7395803360048046</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30114925829419</v>
+        <v>33.49844742023679</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24446410859778</v>
+        <v>34.02069545622101</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490931452354988</v>
+        <v>7.028818311133147</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652780449537743</v>
+        <v>4.622377100030028</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90940672629606</v>
+        <v>11.34275126261653</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29508471910214</v>
+        <v>45.5515121777472</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81735280598795</v>
+        <v>99.76632359144457</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94108599963286</v>
+        <v>87.62652969497677</v>
       </c>
       <c r="C5" t="n">
-        <v>42.315539357525</v>
+        <v>42.93086359302779</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129989020230313</v>
+        <v>2.137492284155907</v>
       </c>
       <c r="E5" t="n">
-        <v>7.068621093578994</v>
+        <v>7.39388119522274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457684412262791</v>
+        <v>0.7412319110495225</v>
       </c>
       <c r="G5" t="n">
-        <v>32.44639478008647</v>
+        <v>32.75412817034572</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30534829640883</v>
+        <v>34.09666790827803</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583911610437741</v>
+        <v>5.870428781865348</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661052757664244</v>
+        <v>4.632699444059515</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05891400036713</v>
+        <v>12.37347030502321</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47302076843135</v>
+        <v>44.50042114886199</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84747412632348</v>
+        <v>99.80475504691299</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.72513990897583</v>
+        <v>86.32711422137348</v>
       </c>
       <c r="C6" t="n">
-        <v>41.81148163480359</v>
+        <v>42.54265541798523</v>
       </c>
       <c r="D6" t="n">
-        <v>2.070910153302933</v>
+        <v>2.075729000767124</v>
       </c>
       <c r="E6" t="n">
-        <v>7.510173508631984</v>
+        <v>7.997113838500555</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746890921247267</v>
+        <v>0.7426347097123724</v>
       </c>
       <c r="G6" t="n">
-        <v>31.54643885483072</v>
+        <v>31.80769083565543</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35698237737427</v>
+        <v>34.16119664676913</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825675835793248</v>
+        <v>4.901282254266551</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668068257795418</v>
+        <v>4.641466935702327</v>
       </c>
       <c r="K6" t="n">
-        <v>15.27486009102417</v>
+        <v>13.67288577862651</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78632739610453</v>
+        <v>43.62139133722533</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87266912193228</v>
+        <v>99.83693253383707</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.24508513902657</v>
+        <v>84.8922031071796</v>
       </c>
       <c r="C7" t="n">
-        <v>40.92570253414605</v>
+        <v>41.86899091686749</v>
       </c>
       <c r="D7" t="n">
-        <v>1.998936175485994</v>
+        <v>2.007830438761601</v>
       </c>
       <c r="E7" t="n">
-        <v>7.781182292664165</v>
+        <v>8.417349728901211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478456038539837</v>
+        <v>0.7438276307979194</v>
       </c>
       <c r="G7" t="n">
-        <v>30.45005005847483</v>
+        <v>30.76723879800548</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40089777728324</v>
+        <v>34.21607101670428</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192138207176956</v>
+        <v>4.0909628015221</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674035024087397</v>
+        <v>4.648922692486996</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75491486097342</v>
+        <v>15.10779689282042</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21311383166407</v>
+        <v>42.88706546102691</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89373122678354</v>
+        <v>99.86385327071481</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.97529079115441</v>
+        <v>83.35776873418629</v>
       </c>
       <c r="C8" t="n">
-        <v>43.17741129784152</v>
+        <v>40.9700015014621</v>
       </c>
       <c r="D8" t="n">
-        <v>2.003139651014024</v>
+        <v>1.935676757774965</v>
       </c>
       <c r="E8" t="n">
-        <v>9.575225447231382</v>
+        <v>8.683827570629134</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494182156927687</v>
+        <v>0.7448430414461676</v>
       </c>
       <c r="G8" t="n">
-        <v>30.9404238752279</v>
+        <v>29.66158291680459</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47323792186735</v>
+        <v>34.2627799065237</v>
       </c>
       <c r="I8" t="n">
-        <v>5.549981832041175</v>
+        <v>3.413789531969188</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683863848079803</v>
+        <v>4.655269009038547</v>
       </c>
       <c r="K8" t="n">
-        <v>12.02470920884559</v>
+        <v>16.64223126581371</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61326830970184</v>
+        <v>42.27412937712636</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81538881638895</v>
+        <v>99.88636214440217</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.76888901050019</v>
+        <v>81.58395582051945</v>
       </c>
       <c r="C9" t="n">
-        <v>41.83263621851756</v>
+        <v>39.72625480798371</v>
       </c>
       <c r="D9" t="n">
-        <v>1.902611806498794</v>
+        <v>1.852590860576024</v>
       </c>
       <c r="E9" t="n">
-        <v>9.866910256953908</v>
+        <v>8.78577703521378</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507676907153247</v>
+        <v>0.7457098023905241</v>
       </c>
       <c r="G9" t="n">
-        <v>29.38767436073964</v>
+        <v>28.38840586434241</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53531377290493</v>
+        <v>34.3026509099641</v>
       </c>
       <c r="I9" t="n">
-        <v>4.633313055716808</v>
+        <v>2.84813508309183</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692298066970778</v>
+        <v>4.660686264940775</v>
       </c>
       <c r="K9" t="n">
-        <v>14.23111098949983</v>
+        <v>18.41604417948056</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78208662998146</v>
+        <v>41.76287352553658</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84583383799885</v>
+        <v>99.90517251300085</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.35236153796588</v>
+        <v>86.16634036161385</v>
       </c>
       <c r="C10" t="n">
-        <v>40.13495234455627</v>
+        <v>42.815371987473</v>
       </c>
       <c r="D10" t="n">
-        <v>1.79367033439822</v>
+        <v>1.85475561535151</v>
       </c>
       <c r="E10" t="n">
-        <v>9.946452644008984</v>
+        <v>10.57097894442387</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519287326761553</v>
+        <v>0.7465811652425192</v>
       </c>
       <c r="G10" t="n">
-        <v>27.70496825351603</v>
+        <v>29.69308607904681</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58872170310314</v>
+        <v>35.61424192752215</v>
       </c>
       <c r="I10" t="n">
-        <v>3.867065291037382</v>
+        <v>3.020564347261241</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69955457922597</v>
+        <v>4.666132282765744</v>
       </c>
       <c r="K10" t="n">
-        <v>16.64763846203412</v>
+        <v>13.83365963838617</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08870605297304</v>
+        <v>43.25040040969309</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87129685956343</v>
+        <v>99.89943203555225</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.70773534611976</v>
+        <v>85.99233539851311</v>
       </c>
       <c r="C11" t="n">
-        <v>38.08948617428625</v>
+        <v>43.04179181133183</v>
       </c>
       <c r="D11" t="n">
-        <v>1.675642547611905</v>
+        <v>1.842263529990253</v>
       </c>
       <c r="E11" t="n">
-        <v>9.829760533691005</v>
+        <v>10.96315873509026</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529308508427303</v>
+        <v>0.7473189409914934</v>
       </c>
       <c r="G11" t="n">
-        <v>25.88191525250584</v>
+        <v>29.53158474845709</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63481913876559</v>
+        <v>35.68792263135602</v>
       </c>
       <c r="I11" t="n">
-        <v>3.226849204935627</v>
+        <v>2.549343431431166</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705817817767064</v>
+        <v>4.670743381196833</v>
       </c>
       <c r="K11" t="n">
-        <v>19.29226465388023</v>
+        <v>14.00766460148687</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51083069152693</v>
+        <v>42.86564936575218</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89258151969341</v>
+        <v>99.9151057785709</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.95931350777032</v>
+        <v>84.16393829160091</v>
       </c>
       <c r="C12" t="n">
-        <v>35.84000084698754</v>
+        <v>41.61000432420454</v>
       </c>
       <c r="D12" t="n">
-        <v>1.554249493309464</v>
+        <v>1.764186560231493</v>
       </c>
       <c r="E12" t="n">
-        <v>9.566326290243213</v>
+        <v>10.85290275483824</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537975390334699</v>
+        <v>0.7479482607268945</v>
       </c>
       <c r="G12" t="n">
-        <v>24.00688244901421</v>
+        <v>28.28000666975208</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67468679553961</v>
+        <v>35.71797554825061</v>
       </c>
       <c r="I12" t="n">
-        <v>2.692136321671164</v>
+        <v>2.126241868258515</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711234618959186</v>
+        <v>4.674676629543089</v>
       </c>
       <c r="K12" t="n">
-        <v>22.04068649222968</v>
+        <v>15.83606170839909</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02967796064567</v>
+        <v>42.48311887207883</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91036529986289</v>
+        <v>99.92918490468244</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.11827916589367</v>
+        <v>85.2497316175438</v>
       </c>
       <c r="C13" t="n">
-        <v>33.41412925217804</v>
+        <v>42.53172825367035</v>
       </c>
       <c r="D13" t="n">
-        <v>1.429968648602906</v>
+        <v>1.765554178541373</v>
       </c>
       <c r="E13" t="n">
-        <v>9.175664460525295</v>
+        <v>11.47021824490395</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545487055046503</v>
+        <v>0.7485280790744951</v>
       </c>
       <c r="G13" t="n">
-        <v>22.08724493754778</v>
+        <v>28.58039885047855</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70924045321391</v>
+        <v>36.02413373051903</v>
       </c>
       <c r="I13" t="n">
-        <v>2.245682551095054</v>
+        <v>1.982598039810796</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715929409404064</v>
+        <v>4.678300494215594</v>
       </c>
       <c r="K13" t="n">
-        <v>24.88172083410633</v>
+        <v>14.7502683824562</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62936834922477</v>
+        <v>42.65196795397806</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92521843550914</v>
+        <v>99.93396459010461</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.4275505795307</v>
+        <v>83.31289065922047</v>
       </c>
       <c r="C14" t="n">
-        <v>38.02826262728247</v>
+        <v>40.90321923353767</v>
       </c>
       <c r="D14" t="n">
-        <v>1.431604107644312</v>
+        <v>1.684891020067633</v>
       </c>
       <c r="E14" t="n">
-        <v>11.71487772349513</v>
+        <v>11.2217195147614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554116849159852</v>
+        <v>0.7490232045137651</v>
       </c>
       <c r="G14" t="n">
-        <v>24.16986213885637</v>
+        <v>27.27464155923334</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80629346520048</v>
+        <v>36.04796244922214</v>
       </c>
       <c r="I14" t="n">
-        <v>2.828178428693537</v>
+        <v>1.653257883211175</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721323030724907</v>
+        <v>4.681395028211031</v>
       </c>
       <c r="K14" t="n">
-        <v>17.5724494204693</v>
+        <v>16.68710934077952</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30512303463141</v>
+        <v>42.35459925791029</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90583508238316</v>
+        <v>99.94492783222748</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.28269531170031</v>
+        <v>82.42849305732678</v>
       </c>
       <c r="C15" t="n">
-        <v>37.31970294662219</v>
+        <v>40.26662021163587</v>
       </c>
       <c r="D15" t="n">
-        <v>1.389025390084829</v>
+        <v>1.648298021593726</v>
       </c>
       <c r="E15" t="n">
-        <v>11.75963682851219</v>
+        <v>11.20918311288122</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756142503966206</v>
+        <v>0.7494433493650229</v>
       </c>
       <c r="G15" t="n">
-        <v>23.45100297383524</v>
+        <v>26.68228222853115</v>
       </c>
       <c r="H15" t="n">
-        <v>36.84190151968189</v>
+        <v>36.0681826049264</v>
       </c>
       <c r="I15" t="n">
-        <v>2.359095445831168</v>
+        <v>1.387082806497876</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725890649788787</v>
+        <v>4.684020933531392</v>
       </c>
       <c r="K15" t="n">
-        <v>18.71730468829967</v>
+        <v>17.57150694267322</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88443185317</v>
+        <v>42.11566267252131</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92143948809186</v>
+        <v>99.9537898268304</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.52905989839776</v>
+        <v>80.13297057525689</v>
       </c>
       <c r="C16" t="n">
-        <v>34.92982442835022</v>
+        <v>38.1863346200926</v>
       </c>
       <c r="D16" t="n">
-        <v>1.285592595944172</v>
+        <v>1.553351241971424</v>
       </c>
       <c r="E16" t="n">
-        <v>11.21188957250816</v>
+        <v>10.75624449685447</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567740119170161</v>
+        <v>0.7498038751455521</v>
       </c>
       <c r="G16" t="n">
-        <v>21.70474060865521</v>
+        <v>25.14530485102821</v>
       </c>
       <c r="H16" t="n">
-        <v>36.87267079083198</v>
+        <v>36.08553349568676</v>
       </c>
       <c r="I16" t="n">
-        <v>1.967554744059863</v>
+        <v>1.156458394910775</v>
       </c>
       <c r="J16" t="n">
-        <v>4.72983757448135</v>
+        <v>4.6862742196597</v>
       </c>
       <c r="K16" t="n">
-        <v>21.47094010160225</v>
+        <v>19.86702942474311</v>
       </c>
       <c r="L16" t="n">
-        <v>43.53370504099665</v>
+        <v>41.90810587720602</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93446957094912</v>
+        <v>99.96146992204173</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.1910016820549</v>
+        <v>84.63098512694225</v>
       </c>
       <c r="C17" t="n">
-        <v>36.14275937358919</v>
+        <v>41.08939894915045</v>
       </c>
       <c r="D17" t="n">
-        <v>1.286636259456425</v>
+        <v>1.554206597210219</v>
       </c>
       <c r="E17" t="n">
-        <v>11.9761040143622</v>
+        <v>12.32181436586042</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573883725050835</v>
+        <v>0.7502167557969756</v>
       </c>
       <c r="G17" t="n">
-        <v>22.15197196593579</v>
+        <v>26.48578717070149</v>
       </c>
       <c r="H17" t="n">
-        <v>37.33221570322907</v>
+        <v>37.43204006900724</v>
       </c>
       <c r="I17" t="n">
-        <v>1.953008038409574</v>
+        <v>1.398065444634816</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733677328156772</v>
+        <v>4.688854723731096</v>
       </c>
       <c r="K17" t="n">
-        <v>19.80899831794508</v>
+        <v>15.36901487305776</v>
       </c>
       <c r="L17" t="n">
-        <v>43.98319484703169</v>
+        <v>43.49500964374373</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93495253856597</v>
+        <v>99.95342346595193</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.5838724786571</v>
+        <v>86.19840424163453</v>
       </c>
       <c r="C18" t="n">
-        <v>33.83622252530744</v>
+        <v>41.83346406738048</v>
       </c>
       <c r="D18" t="n">
-        <v>1.192751827654342</v>
+        <v>1.555512901440174</v>
       </c>
       <c r="E18" t="n">
-        <v>11.37366180559635</v>
+        <v>12.93428350125249</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579183439808851</v>
+        <v>0.7508473098836975</v>
       </c>
       <c r="G18" t="n">
-        <v>20.53556695167311</v>
+        <v>26.62798120868482</v>
       </c>
       <c r="H18" t="n">
-        <v>37.35833837710343</v>
+        <v>37.4635015441842</v>
       </c>
       <c r="I18" t="n">
-        <v>1.628645522768446</v>
+        <v>2.173482089416043</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736989649880532</v>
+        <v>4.692795686773109</v>
       </c>
       <c r="K18" t="n">
-        <v>22.41612752134291</v>
+        <v>13.80159575836547</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69339973006048</v>
+        <v>44.29255161356001</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94574977671084</v>
+        <v>99.92761143930596</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.50404817875599</v>
+        <v>83.67650055644235</v>
       </c>
       <c r="C19" t="n">
-        <v>32.9878965336159</v>
+        <v>39.6485937484879</v>
       </c>
       <c r="D19" t="n">
-        <v>1.153765065410313</v>
+        <v>1.461161867650586</v>
       </c>
       <c r="E19" t="n">
-        <v>11.23120022994918</v>
+        <v>12.45183338226519</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583726795483686</v>
+        <v>0.7513894545023833</v>
       </c>
       <c r="G19" t="n">
-        <v>19.86433321492359</v>
+        <v>25.01283706398305</v>
       </c>
       <c r="H19" t="n">
-        <v>37.38073290284832</v>
+        <v>37.4905518318951</v>
       </c>
       <c r="I19" t="n">
-        <v>1.375814838898938</v>
+        <v>1.812542865506154</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739829247177304</v>
+        <v>4.696184090639894</v>
       </c>
       <c r="K19" t="n">
-        <v>23.49595182124398</v>
+        <v>16.32349944355763</v>
       </c>
       <c r="L19" t="n">
-        <v>43.47031862519961</v>
+        <v>43.96753230547068</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95416698005948</v>
+        <v>99.93962549751623</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>73.76948812334695</v>
+        <v>81.08032765742394</v>
       </c>
       <c r="C20" t="n">
-        <v>30.46419652871391</v>
+        <v>37.3327909340364</v>
       </c>
       <c r="D20" t="n">
-        <v>1.056479564649205</v>
+        <v>1.364556480113625</v>
       </c>
       <c r="E20" t="n">
-        <v>10.47536956964155</v>
+        <v>11.88047318887998</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587657663362092</v>
+        <v>0.7518563343767189</v>
       </c>
       <c r="G20" t="n">
-        <v>18.1893721140585</v>
+        <v>23.35910186088042</v>
       </c>
       <c r="H20" t="n">
-        <v>37.40010843234742</v>
+        <v>37.51384678769088</v>
       </c>
       <c r="I20" t="n">
-        <v>1.147106636712753</v>
+        <v>1.511390915627816</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742286039601307</v>
+        <v>4.699102089854493</v>
       </c>
       <c r="K20" t="n">
-        <v>26.23051187665304</v>
+        <v>18.91967234257607</v>
       </c>
       <c r="L20" t="n">
-        <v>43.26707451577474</v>
+        <v>43.69718831045679</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96178292114169</v>
+        <v>99.94965158706925</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.16821531783935</v>
+        <v>78.36981060329185</v>
       </c>
       <c r="C21" t="n">
-        <v>34.52983336107012</v>
+        <v>34.85538621506699</v>
       </c>
       <c r="D21" t="n">
-        <v>1.057160217073039</v>
+        <v>1.264189008871128</v>
       </c>
       <c r="E21" t="n">
-        <v>12.63747010487629</v>
+        <v>11.21665449910686</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759254612287669</v>
+        <v>0.7522593232808824</v>
       </c>
       <c r="G21" t="n">
-        <v>20.09819477740934</v>
+        <v>21.6409655884432</v>
       </c>
       <c r="H21" t="n">
-        <v>39.32130789377009</v>
+        <v>37.53395390565572</v>
       </c>
       <c r="I21" t="n">
-        <v>1.549486385624996</v>
+        <v>1.260167507428553</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745341326797932</v>
+        <v>4.701620770505515</v>
       </c>
       <c r="K21" t="n">
-        <v>19.83178468216065</v>
+        <v>21.63018939670813</v>
       </c>
       <c r="L21" t="n">
-        <v>45.58676566513314</v>
+        <v>43.47244130723522</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94838370836391</v>
+        <v>99.95801691901035</v>
       </c>
     </row>
   </sheetData>
